--- a/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N68_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6588_W0053F0003T0006Z000C1N68_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.86327781775973</v>
+        <v>7.615282645385957</v>
       </c>
       <c r="D2" t="n">
-        <v>28.17164199250314</v>
+        <v>4.57789182378176</v>
       </c>
       <c r="E2" t="n">
-        <v>20.26813788149593</v>
+        <v>3.293572405743089</v>
       </c>
       <c r="F2" t="n">
-        <v>7.606783263293261</v>
+        <v>1.236102280285155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.14345036935376</v>
+        <v>9.610810685019986</v>
       </c>
       <c r="D3" t="n">
-        <v>17.02640232564911</v>
+        <v>2.766790377917981</v>
       </c>
       <c r="E3" t="n">
-        <v>20.26813788149593</v>
+        <v>3.293572405743089</v>
       </c>
       <c r="F3" t="n">
-        <v>7.606783263293261</v>
+        <v>1.236102280285155</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.869743635762889</v>
+        <v>1.60383334081147</v>
       </c>
       <c r="D4" t="n">
-        <v>26.26769445207263</v>
+        <v>4.268500348461802</v>
       </c>
       <c r="E4" t="n">
-        <v>20.26813788149593</v>
+        <v>3.293572405743089</v>
       </c>
       <c r="F4" t="n">
-        <v>7.606783263293261</v>
+        <v>1.236102280285155</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.60919760794632</v>
+        <v>2.048994611291277</v>
       </c>
       <c r="D5" t="n">
-        <v>18.02045821713437</v>
+        <v>2.928324460284335</v>
       </c>
       <c r="E5" t="n">
-        <v>20.26813788149593</v>
+        <v>3.293572405743089</v>
       </c>
       <c r="F5" t="n">
-        <v>7.606783263293261</v>
+        <v>1.236102280285155</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5.047675201843975</v>
+        <v>0.820247220299646</v>
       </c>
       <c r="D6" t="n">
-        <v>19.94296314537594</v>
+        <v>3.24073151112359</v>
       </c>
       <c r="E6" t="n">
-        <v>20.26813788149593</v>
+        <v>3.293572405743089</v>
       </c>
       <c r="F6" t="n">
-        <v>7.606783263293261</v>
+        <v>1.236102280285155</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2.836089345873597</v>
+        <v>0.4608645187044595</v>
       </c>
       <c r="D7" t="n">
-        <v>19.21776038634392</v>
+        <v>3.122886062780887</v>
       </c>
       <c r="E7" t="n">
-        <v>20.26813788149593</v>
+        <v>3.293572405743089</v>
       </c>
       <c r="F7" t="n">
-        <v>7.606783263293261</v>
+        <v>1.236102280285155</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>3.625521793213215</v>
+        <v>0.5891472913971474</v>
       </c>
       <c r="D8" t="n">
-        <v>1.145532258936577</v>
+        <v>0.1861489920771937</v>
       </c>
       <c r="E8" t="n">
-        <v>20.26813788149593</v>
+        <v>3.293572405743089</v>
       </c>
       <c r="F8" t="n">
-        <v>7.606783263293261</v>
+        <v>1.236102280285155</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.91435594933383</v>
+        <v>1.611082841766747</v>
       </c>
       <c r="D9" t="n">
-        <v>16.73279448692637</v>
+        <v>2.719079104125535</v>
       </c>
       <c r="E9" t="n">
-        <v>20.26813788149593</v>
+        <v>3.293572405743089</v>
       </c>
       <c r="F9" t="n">
-        <v>7.606783263293261</v>
+        <v>1.236102280285155</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
